--- a/Phase6.2/quantized (Cleaned)/load_42.xlsx
+++ b/Phase6.2/quantized (Cleaned)/load_42.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8720"/>
+    <workbookView windowWidth="18350" windowHeight="8720"/>
   </bookViews>
   <sheets>
     <sheet name="Timestamp logs" sheetId="1" r:id="rId1"/>
@@ -34,14 +34,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -497,28 +490,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -527,118 +523,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -703,6 +696,9379 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Sensing Unit Program: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$A$1:$A$497</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="497"/>
+                <c:pt idx="0">
+                  <c:v>30.6608</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22.9971</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16.9457</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.4242</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23.5251</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>23.9467</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16.0308</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15.8239</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>21.3151</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>25.3901</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>14.7534</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>15.7775</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>19.3949</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>23.2171</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>21.1932</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15.9241</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>19.2936</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>23.0816</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>22.9494</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>17.3811</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>18.7944</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>24.1097</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>17.887</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>17.8154</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>17.3452</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>21.729</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26.9534</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>17.7839</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>17.16</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>19.5911</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>23.1653</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>15.9727</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>16.795</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>24.4093</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>19.2338</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>24.0254</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>19.3395</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>21.183</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>26.614</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>17.9845</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>15.2339</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>30.3581</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>21.9101</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>16.9969</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>15.0448</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>22.2202</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>21.7009</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>26.6484</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>19.8707</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>29.6718</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>20.2775</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>22.0666</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>49.2257</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>23.2754</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>20.0498</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>24.2526</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>37.6355</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>20.6322</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>19.2504</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>19.9644</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>40.6973</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>23.1436</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>47.8363</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>53.4079</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>18.5058</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>17.6808</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>34.3899</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>21.2716</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>37.8792</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>22.7126</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>19.0937</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>43.362</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>47.2989</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>34.9418</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>32.5635</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>14.5237</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>16.0021</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>45.2188</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>24.451</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>40.9184</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>34.53</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>33.6935</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>14.7262</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>35.2029</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>19.3245</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>46.5034</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>16.7526</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>27.4933</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>41.2539</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>45.2965</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>20.1268</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>46.2691</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>25.2092</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>22.7071</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>25.3367</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>23.9031</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>20.7312</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>19.5841</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>39.2843</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>30.2054</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>50.9405</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>47.5925</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>19.2408</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>20.5818</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>24.8117</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>17.1983</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>21.3723</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>30.3893</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>23.0654</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>20.6645</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>17.6855</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>35.4297</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>23.033</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>17.7862</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>36.5337</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>19.9152</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>25.3822</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>26.0012</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>23.9677</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>39.5715</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>26.341</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>37.3007</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>15.2314</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>18.6134</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>38.6804</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>23.0172</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>18.9338</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>20.7511</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>22.391</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>23.4306</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>42.2963</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>30.0356</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>39.2576</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>19.4662</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>20.3567</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>29.733</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>51.0969</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>22.3803</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>29.2664</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>23.8705</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>27.7776</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>25.7624</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>27.2485</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>33.15</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>19.3404</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>17.2413</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>15.0267</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>27.2351</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>25.1592</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>15.7975</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>29.9039</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>24.0407</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>37.6888</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>16.8763</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>26.3576</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>18.2268</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>42.8531</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>25.8866</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>17.9476</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>46.3019</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>33.3737</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>17.3648</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>17.4927</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>43.3582</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>26.2616</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>34.0784</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>16.685</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>44.7929</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>16.7105</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>18.2247</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>24.4626</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>21.4745</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>46.2359</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>20.3257</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>44.3821</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>15.6471</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>22.8978</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>24.979</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>17.3597</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>16.7015</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>28.1377</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>32.5892</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>48.7741</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>25.8503</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>17.1324</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>34.1163</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>34.8372</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>28.6832</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>29.5684</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>28.1459</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>33.335</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>53.5945</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>24.7299</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>30.8912</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>20.9737</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>42.1638</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>23.2643</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>30.1465</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>19.9088</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>34.2729</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>18.974</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>20.8294</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>26.8368</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>53.7536</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>15.6462</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>42.7031</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>16.7204</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>34.0856</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>20.6268</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>23.5853</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>18.1084</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>13.8999</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>22.7337</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>27.9085</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>13.3355</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>12.3771</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>12.1714</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>19.4534</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>28.3715</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>22.8313</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>14.4684</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>19.6715</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>16.6611</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>22.0543</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>20.1529</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>35.7368</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>20.1623</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>19.3766</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>31.8576</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>18.0574</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>30.4284</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>20.3898</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>54.1079</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>61.4936</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>27.7299</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>22.1387</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>24.7761</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>45.5837</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>16.0433</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>39.1546</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>17.9684</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>30.0699</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>32.8805</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>19.4501</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>35.7726</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>28.8014</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>25.1976</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>20.2558</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>27.4398</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>155.1459</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>19.7096</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>40.2405</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>55.572</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>20.4577</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>35.215</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>31.4265</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>18.4855</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>41.8388</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>18.6867</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>32.3344</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>26.259</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>21.2631</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>34.9622</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>20.4215</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>22.0073</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>25.2601</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>54.9805</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>18.7065</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>32.2783</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>16.7184</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>23.3417</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>24.9088</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>27.6794</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>40.7326</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>21.5809</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>18.6982</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>24.8769</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>35.2643</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>30.7236</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>27.5898</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>17.8728</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>32.9227</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>26.5088</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>37.4338</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>29.6888</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>47.3675</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>16.1197</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>25.6668</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>17.413</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>42.4681</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>25.0913</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>17.1667</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>18.5165</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>21.6233</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>27.8136</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>21.8439</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>21.865</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>19.5796</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>32.4716</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>18.8245</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>31.6086</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>23.3259</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>41.0149</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>132.2808</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>33.392</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>26.9168</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>21.6258</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>14.7245</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>18.2285</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>19.9393</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>34.1887</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>25.714</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>22.5875</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>25.0459</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>47.5324</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>25.71</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>47.7475</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>20.4088</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>39.3892</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>19.4322</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>17.4085</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>42.2529</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>21.7246</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>46.8631</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>23.5649</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>37.0692</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>34.979</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>17.3162</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>21.2468</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>41.0121</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>33.1165</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>18.9307</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>40.4724</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>31.0796</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>20.2285</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>46.6449</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>24.25</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>37.0286</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>18.5609</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>37.0203</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>16.0453</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>30.7129</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>47.8024</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>20.0548</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>40.9864</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>32.3144</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>25.2199</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>21.6667</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>46.2866</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>40.7891</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>41.124</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>20.0521</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>22.7907</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>36.2357</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>24.0905</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>26.0994</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>33.4323</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>32.9035</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>29.8918</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>32.3325</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>34.0803</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>17.6848</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>46.0754</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>22.4754</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>17.9329</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>34.3626</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>17.8879</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>24.4418</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>26.2976</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>22.5039</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>15.848</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>14.9765</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>29.2538</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>17.8779</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>43.9922</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>23.545</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>33.235</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>24.4148</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>37.0755</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>15.2395</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>37.9023</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>24.0625</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>32.7036</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>20.9509</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>23.0016</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>40.0686</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>35.6625</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>24.2742</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>38.9802</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>38.9879</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>17.239</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>56.7262</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>18.1658</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>24.1504</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>26.24</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>20.444</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>21.0568</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>30.8421</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>29.5061</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>24.986</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>28.5688</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>19.8563</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>28.5386</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>59.1668</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>23.4104</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>32.1284</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>21.6719</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>14.0964</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>19.7484</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>13.2003</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>23.8304</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>16.7492</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>21.4994</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>18.8908</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>12.8683</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>13.6944</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>13.0936</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>20.3931</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>19.4714</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>10.3646</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>10.1143</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>15.4373</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>14.645</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>29.2965</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>18.7662</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>9.847</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>19.7343</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>29.4144</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>30.8008</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>10.282</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>11.0291</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>10.8278</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>11.3388</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>23.7295</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>11.0323</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>12.0033</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>15.5678</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>135.9248</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>28.6672</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>15.0093</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>17.8766</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>24.5067</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>17.5927</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>34.0156</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>20.1391</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>34.0447</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>39.7192</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>28.0208</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>21.8383</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>43.9486</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>20.5466</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>25.7625</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>20.4111</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>20.6412</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>12.7861</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>12.1541</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>23.4381</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>15.6643</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>15.4106</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>24.9503</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>10.4158</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>21.877</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>28.5674</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>11.0205</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>12.8019</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>28.6597</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>18.6299</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>27.0609</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>22.5054</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>37.2053</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>35.4548</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>18.9611</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>15.8459</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>49.7822</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>17.9784</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>44.6072</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>26.2389</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>24.2302</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>59.2409</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>32.5338</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>32.2154</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>27.2886</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>20.272</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>24.3734</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>31.8157</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>27.4336</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>20.3736</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>20.5836</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>34.8758</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>31.848</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>37.124</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>20.46</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>22.1809</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>41.1342</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>24.1928</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>29.6682</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="982501314"/>
+        <c:axId val="854169971"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="982501314"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="854169971"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="854169971"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="982501314"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Queue Lifetime: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$B$1:$B$497</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="497"/>
+                <c:pt idx="0">
+                  <c:v>0.114274</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.105792</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>148.58617</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>317.245448</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>297.25965</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>394.957904</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>522.446207</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>533.749715</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>691.155817</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>672.496782</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>735.014775</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>760.826067</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1096.088337</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1184.279215</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1183.119028</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1269.818022</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1329.27818</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1773.740385</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1792.862672</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1840.510906</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1947.242958</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2200.981815</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2291.021516</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2336.60809</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2619.762203</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2632.076109</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2673.000536</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2651.495159</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2858.591144</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3226.840585</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3257.671889</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3462.655827</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3521.40456</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3506.349076</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3521.188599</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>4054.482195</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>4215.453057</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>4297.082468</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>4307.353258</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>4366.81693</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>4670.474921</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>4696.808674</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>4791.598757</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>4793.552757</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>4941.392271</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>5045.606454</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>5311.576725</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>5441.578727</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>5442.213393</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>5311.993235</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>5357.667712</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>5349.714288</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>5545.79876</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>5607.876878</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5401.983271</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5645.011315</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5570.47408</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5544.939076</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5448.734318</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>5456.131537</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>5314.362585</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5414.477438</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>5488.691229</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5287.886137</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>5565.611958</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>5660.007743</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>5395.814599</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>5437.363047</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>5292.437092</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>5392.711416</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>5547.803138</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>5420.350187</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>5180.135965</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>5115.914306</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>5191.104665</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>5082.588838</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>5240.584839</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>5049.897642</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>5160.86485</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>5066.576952</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>5056.180543</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>5135.932287</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>5086.220316</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>5076.430572</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>4935.965784</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>5011.666339</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>5050.526303</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>4939.714757</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>5191.354778</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>5078.664742</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>4921.328164</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>4798.870503</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>4838.398577</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>4813.40811</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>4990.031106</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>4909.709239</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>4878.583046</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>5046.833693</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>4688.735706</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>5035.438577</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>5042.910564</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>4781.493016</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>4749.012318</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>4912.769934</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>5012.971564</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>4991.334684</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>5023.442053</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>4760.056647</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>5051.752846</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>5051.345735</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>4923.216612</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>4796.816794</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>4962.481848</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>4863.288124</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>5106.95731</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>5059.314557</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>4933.6539</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4952.373372</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>5026.532643</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>5187.851528</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>4962.400972</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>4981.833989</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>4991.993532</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>5232.107906</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>5209.010275</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>5110.6182</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>5166.811249</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>5164.149864</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>5233.320587</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>5543.439466</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>5288.998371</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>5028.652685</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>4898.795924</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>4881.905232</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>5436.427405</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>5351.582153</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>5072.44072</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>4847.802031</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>4883.335229</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>4988.908233</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>5001.134411</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>4862.195392</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>4847.150108</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>4781.694891</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>4830.354053</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>4964.036995</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>5004.392209</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>4881.3368</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>5064.087114</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>4961.700321</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>5282.170464</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>5138.616267</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>5002.715557</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>5046.71921</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>5423.646186</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>5214.761706</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>5093.146782</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>5071.131172</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>5209.71507</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>5344.794504</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>5338.38406</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>5284.062086</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>5376.844641</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>5166.765942</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>5132.503931</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>5340.92275</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>5135.11643</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>5156.401583</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>5241.618957</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>5238.756855</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>5434.470427</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>5264.791165</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>5358.313991</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>5428.425626</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>5381.251189</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>5468.685949</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>5499.192421</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>5560.035807</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>5564.207739</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>5540.254588</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>5429.825133</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>5749.810994</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>5378.789926</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>5377.445696</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>5560.011114</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>5621.35932</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>5762.273374</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>5535.829951</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>5339.254869</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>5440.251329</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>5574.053954</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>5353.498234</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>5134.527816</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>5386.554787</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>5432.897756</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>5323.028174</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>5463.786022</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>5367.872817</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>5342.523951</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>5255.745052</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>5351.992734</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>5331.257903</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>5246.541221</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>5486.865169</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>5467.498955</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>5383.686498</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>5276.007874</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>5177.749402</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>5356.954531</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>5061.721326</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>5262.000582</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>5244.594107</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>5093.713026</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>4983.450752</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>4863.49474</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>4986.75928</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>5533.844854</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>5582.302153</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>5279.042974</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>5361.112139</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>5369.399895</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>5380.161231</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>5222.29981</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>5292.431592</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>5226.340485</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>5183.819451</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>5507.376576</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>5352.997023</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>5192.46165</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>5433.196833</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>5361.826092</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>5493.4557</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>5570.313735</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>5312.77721</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>5406.080115</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>5434.836717</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>5425.718545</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>5360.74879</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>5469.127185</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>5673.793538</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>5340.15436</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>5263.12097</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>5624.361176</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>5664.59133</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>5775.186248</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>5492.954199</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>5535.358186</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>5359.244405</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>5622.756207</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>5718.630174</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>5568.396591</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>5610.128428</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>5868.082454</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>5349.677041</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>5551.54045</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>5797.041287</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>5925.92901</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>5922.269804</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>5558.165514</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>5568.216027</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>5814.821388</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>5776.011045</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>5965.865999</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>5480.78642</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>5570.878682</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>6086.648654</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>5881.121463</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>5779.569731</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>5725.760599</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>5706.861873</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>5971.776974</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>5736.283299</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>5602.650392</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>5627.640939</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>5499.791845</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>5919.901592</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>5857.994866</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>5750.797917</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>5813.598039</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>5809.128638</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>5694.697887</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>5753.537616</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>5701.037009</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>5870.578023</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>5990.494862</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>5784.415824</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>5873.341802</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>6012.694539</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>6041.000012</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>5767.436802</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>6016.838977</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>5830.461594</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>5619.441028</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>5471.643496</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>5855.720439</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>5883.562552</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>5854.681744</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>5629.190781</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>5749.302685</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>5628.532129</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>5580.846509</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>5907.092461</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>5754.337292</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>5686.488986</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>5684.658888</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>5622.982897</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>5837.642281</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>5710.936165</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>5751.237515</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>6053.764462</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>6050.6052</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>6172.667674</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>5846.660288</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>6062.3482</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>6119.207127</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>6005.931233</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>5842.666427</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>5759.154908</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>6056.405731</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>5987.184901</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>6145.726681</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>5924.190954</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>5919.258249</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>5770.378427</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>5886.405237</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>5922.688106</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>5976.739336</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>5567.329529</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>5575.895651</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>5956.640586</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>5983.447945</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>5706.070927</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>5675.987182</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>5607.096031</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>5936.363108</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>5930.410074</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>5882.682438</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>5968.813089</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>5676.04492</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>5824.572114</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>5790.278276</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>5774.574031</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>5925.241007</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>5660.202776</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>5733.807713</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>5928.443747</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>5706.334469</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>5699.98427</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>5927.486261</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>5901.096815</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>5486.635671</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>5397.8351</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>5533.041624</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>5982.575161</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>5966.269995</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>5750.915769</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>5854.962112</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>5538.494722</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>5773.997227</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>5843.551277</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>5654.928729</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>5509.389963</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>5667.872297</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>5488.215751</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>5534.172952</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>5622.287728</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>5374.016815</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>5269.014602</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>5422.301122</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>5331.82699</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>5619.861186</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>5346.703344</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>5369.872837</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>5314.920365</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>5332.088154</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>5212.824434</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>5231.795167</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>5272.342435</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>5454.636606</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>5318.009588</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>4977.307289</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>4878.442218</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>4768.074085</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>4957.552164</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>4969.845704</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>4627.478708</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>4634.772837</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>4769.537282</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>4751.980471</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>4678.265515</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>4275.86002</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>4258.869369</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>4465.912225</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>4458.215673</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>4620.973544</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>4531.770863</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>4365.0791</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>4336.780325</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>4388.914859</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>4511.173322</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>4416.912402</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>4428.131744</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>4330.600871</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>4450.899971</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>4493.844734</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>4365.98136</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>4755.894644</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>4362.772479</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>4424.830869</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>4431.860762</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>4655.928738</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>4485.548151</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>4544.986183</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>4568.337139</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>4527.93932</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>4475.412593</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>4760.389046</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>4765.752301</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>4902.823141</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>4890.59354</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>4736.624238</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>4762.269876</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>4981.850036</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>4971.248982</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>4883.045595</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>4958.803449</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>5114.55112</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>5190.049259</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>5188.651674</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>4919.577312</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>5027.16914</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>4872.975222</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>4919.237451</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>4974.471654</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>4998.840821</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>5061.329898</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>5075.467153</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>4989.399641</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>4780.957334</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>4970.514267</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>5066.09132</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>5064.701644</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>5037.740753</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>4840.053441</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>4866.744116</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>5117.061762</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>5115.196221</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>4798.595358</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>4886.029974</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>4833.26028</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>5109.469626</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>5013.103717</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>5036.723312</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>5156.356583</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>5015.2065</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>4939.058301</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>5050.921474</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>5261.125998</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>5358.050333</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>5071.254448</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>5095.984415</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>5059.900926</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>5264.42887</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>5142.76767</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>5079.477639</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>5043.08843</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>5021.798096</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>5272.481319</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>5488.023</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>5545.039196</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>5265.070835</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>5305.251599</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>5711.837702</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>5654.766597</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>5706.220953</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>5554.642511</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>5520.930709</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>5661.640796</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>5859.030043</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>5759.505089</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>5614.362857</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>5581.209371</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>5571.242694</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>5713.030048</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>6043.382593</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>5834.032252</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>5858.546132</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>5976.508957</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>6097.800281</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>6010.581163</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>5896.65966</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>5968.742881</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>6232.844723</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>6313.497255</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>6076.194716</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>5985.249025</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>6018.517836</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="312925375"/>
+        <c:axId val="762483304"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="312925375"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="762483304"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="762483304"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="312925375"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Inference Program: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$C$1:$C$497</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="497"/>
+                <c:pt idx="0">
+                  <c:v>753.237794</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>254.207912</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500.889506</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>493.791001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>497.364222</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500.101116</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>303.359805</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1005.71702</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>443.991588</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>601.049999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>646.93956</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>494.218435</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>707.438729</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>799.829364</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>707.008499</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>798.138143</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>998.23086</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>703.909699</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>506.062376</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>999.817552</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>753.079414</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>591.718718</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>409.688429</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>641.473279</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>788.784247</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>691.602903</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>994.628535</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>903.187999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>754.404035</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>411.877961</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1095.289482</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1093.802112</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>803.817536</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>532.029262</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>886.632593</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1103.117016</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>500.07584</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>505.662983</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>610.042874</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>509.129382</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>501.624176</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>893.014231</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>789.527159</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>589.185025</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>902.400637</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>601.314277</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>496.142929</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>607.691882</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>863.26275</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>800.057653</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1095.079925</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>905.161136</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>706.461538</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>704.799804</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>703.953263</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>410.69041</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>700.567207</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>898.655165</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1000.775294</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>538.171332</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>988.437612</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>801.617742</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>599.820404</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>697.366674</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>701.038791</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>605.183859</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>299.452731</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>590.952129</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>804.451906</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>547.502188</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>694.340041</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>493.289991</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>610.375494</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>697.416441</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>601.745618</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>497.60374</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>619.31243</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>803.905478</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>410.791648</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>702.175634</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>587.862842</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>678.35419</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>583.684345</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>795.48254</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>775.879519</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>497.57268</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>798.102275</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>502.103272</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>603.607243</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>804.193691</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>797.805778</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>697.905259</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>590.543456</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>542.837417</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>700.719898</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>901.254091</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>1003.742679</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>1005.634182</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>648.499496</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>610.423876</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>598.420469</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>697.564936</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>589.188841</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>891.228507</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>501.578589</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>550.691153</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>502.40132</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>696.728005</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>400.619346</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>648.591117</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>790.900808</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>701.001276</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>801.907213</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>500.70848</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>900.543842</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>603.74843</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>597.906712</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>603.312354</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>801.72546</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>991.122395</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>603.454256</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>694.019195</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>796.37861</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>1010.37202</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>492.036329</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>804.831488</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>598.439317</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>604.686135</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>500.440141</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>705.793578</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>806.411801</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>887.09294</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>505.70107</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>640.845007</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>508.561135</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>702.782394</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>493.83563</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>496.859568</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>696.776094</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>397.872577</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>798.437703</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>699.045981</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>648.456889</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>792.83613</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>703.331656</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>993.103829</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>454.084898</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>799.83459</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>1103.644208</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>599.365021</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>796.981862</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>871.1444</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>701.081276</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>604.653263</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>991.293944</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>551.428005</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>996.622144</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>695.700261</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>845.287518</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>559.825506</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>599.16112</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>705.967847</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>756.270005</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>731.834791</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>560.67193</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>705.325384</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>1098.571798</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>554.31829</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>700.629108</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>896.808848</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>792.686065</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>1041.444094</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>594.769045</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>707.273986</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>699.595139</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>600.274913</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>702.158315</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>901.392717</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>1007.717048</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>490.829416</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>597.40656</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>894.288567</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>704.592441</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>602.412717</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>707.593329</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>792.196605</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>989.793498</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>401.99079</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>506.869346</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>693.065375</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>401.026341</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>800.229889</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>996.059929</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>397.627307</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>804.756109</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>899.147354</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>588.434296</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>599.130529</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>896.562947</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>808.495071</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>596.579074</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>698.122754</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>596.057493</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>871.043774</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>498.070008</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>903.224318</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>349.068796</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>703.575446</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>600.308089</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>406.702916</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>1195.744865</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>1090.432958</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>504.582986</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>1002.149613</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>906.472093</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>888.813624</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>692.873616</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>551.901351</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>822.545793</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>704.148101</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>501.262021</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>796.686526</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>700.486488</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>597.168464</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>1001.282376</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>800.493659</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>800.249511</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>802.134041</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>647.582322</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>1068.834701</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>897.716505</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>401.5952</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>891.250913</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>693.889256</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>806.821973</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>626.725159</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>995.633779</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>401.890053</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>798.771431</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>699.475256</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>840.274304</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>698.110834</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>594.635925</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>804.506203</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>798.871744</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>794.93493</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>755.186737</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>998.921612</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>792.524441</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>896.939704</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>1107.615067</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>1260.929681</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>898.263892</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>799.407225</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>701.028685</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>805.207459</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>489.248433</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>705.859258</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>697.637689</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>699.75584</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>897.354922</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>795.584611</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>854.815011</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>794.827232</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>900.202046</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>605.499959</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>648.337829</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>694.828223</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>544.357519</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>494.159863</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>1004.281728</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>801.594282</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>557.770279</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>1197.742749</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>694.618929</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>807.883727</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>910.400585</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>600.187996</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>402.27137</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>794.646837</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>1297.910578</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>706.033693</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>891.5477</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>859.552774</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>1100.182136</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>594.824681</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>798.359515</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>829.06647</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>639.219851</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>910.219277</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>763.912493</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>902.819344</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>601.488783</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>565.985012</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>500.415109</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>448.311933</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>974.839396</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>789.339676</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>1010.998841</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>606.732224</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>840.620008</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>900.373655</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>702.530234</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>774.094674</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>1253.082303</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>992.566006</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>691.327258</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>497.720181</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>1103.319696</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>795.138055</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>798.849828</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>803.101979</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>600.746317</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>1004.828696</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>598.370816</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>506.23098</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>997.834608</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>894.392929</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>604.409901</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>913.09094</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>866.349832</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>800.71249</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>501.983225</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>696.427348</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>981.834832</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>660.500539</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>922.210765</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>608.705692</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>699.846053</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>738.903492</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>704.724673</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>595.490457</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>803.6359</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>870.621061</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>856.984197</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>700.596972</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>706.232726</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>788.05454</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>798.983685</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>794.995379</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>991.90388</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>1099.436769</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>607.388862</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>1005.358343</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>800.14323</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>602.694335</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>703.486242</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>495.866644</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>893.687721</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>806.806703</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>674.132827</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>999.365439</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>709.592247</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>930.904425</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>705.249989</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>495.094676</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>900.46202</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>447.463044</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>499.557772</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>445.822631</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>500.223989</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>893.516778</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>407.179401</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>301.213521</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>598.958422</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>805.935905</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>601.392295</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>798.964405</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>600.096763</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>1154.246406</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>494.841763</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>697.863996</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>390.509048</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>896.177148</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>695.432954</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>604.475308</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>411.214912</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>359.861147</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>399.961553</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>883.319838</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>495.719899</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>499.377154</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>503.103549</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>532.30907</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>402.920605</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>409.460474</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>488.67038</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>493.661871</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>491.985188</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>711.578184</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>892.874427</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>948.896328</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>497.197477</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>406.925107</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>1084.862266</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>502.193844</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>599.98969</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>474.695301</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>351.891979</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>526.756855</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>500.585454</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>857.919716</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>904.233498</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>695.097441</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>1200.108272</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>600.342047</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>958.943891</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>493.776582</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>704.228818</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>495.768792</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>596.833758</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>799.156765</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>668.69536</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>700.680943</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>741.991902</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>607.151251</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>777.109248</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>496.961688</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>604.666603</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>1054.188735</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>610.145141</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>596.970304</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>992.593939</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>598.858544</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>592.421323</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>499.678386</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>397.632425</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>405.865919</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>609.157101</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>506.754338</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>901.111424</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>600.143104</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>607.142016</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>495.941283</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>696.50913</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>696.097378</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>597.754602</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>692.398411</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>894.968192</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>590.708549</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>893.823439</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>698.318106</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>702.207475</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>796.713099</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>595.028132</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>1200.927614</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>596.282515</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>645.405941</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>697.543483</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>807.353074</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>700.902056</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>503.003226</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>797.633557</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>904.295823</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>697.644923</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>800.234728</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>503.161101</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>803.549942</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>700.748815</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>604.184256</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>709.286377</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>615.9195</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>878.791946</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>593.30715</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>902.778572</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>787.163337</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>782.388914</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>1052.497649</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>896.228652</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>1004.908725</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>1106.786609</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>711.469792</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>743.278811</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>902.5839</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>899.907708</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>703.11219</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>687.607188</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>547.087126</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>575.945943</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>803.324224</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>991.492505</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>801.592855</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>1201.133493</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>1090.296666</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>805.230867</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>798.642474</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>992.037139</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>1202.143062</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>708.60299</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>793.486834</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>803.222283</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>794.418366</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>603.972877</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>600.59314</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>507.959477</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>492.213334</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>497.723065</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="599596895"/>
+        <c:axId val="526381824"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="599596895"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="526381824"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="526381824"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="599596895"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Entire Pipeline: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$D$1:$D$497</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="497"/>
+                <c:pt idx="0">
+                  <c:v>784.012868</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>277.310804</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>666.421376</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>829.460649</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>818.148972</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>919.00572</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>841.836812</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1555.290635</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1156.462505</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1298.936881</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1396.707735</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1270.822002</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1822.921966</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2007.325679</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1911.320727</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2083.880265</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2346.80264</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2500.731684</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2321.874448</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2857.709558</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2719.116772</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2816.810233</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2718.596945</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2995.896769</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3425.89165</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3345.408012</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3694.582471</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3572.467058</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3630.155179</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3658.309646</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>4376.126671</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>4572.430639</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>4342.017096</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>4062.787638</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>4427.054992</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>5181.624611</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>4734.868397</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>4823.928451</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>4944.010132</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>4893.930812</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>5187.332997</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>5620.181005</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>5603.036016</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>5399.734682</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>5858.837708</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>5669.140931</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>5829.420554</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>6075.919009</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>6325.346843</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>6141.722688</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>6473.025137</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>6276.942024</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>6301.485998</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>6335.952082</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>6125.986334</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>6079.954325</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>6308.676787</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>6464.226441</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>6468.760012</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>6014.267269</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>6343.497497</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>6239.23878</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6136.347933</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>6038.660711</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>6285.156549</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>6282.872402</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>5729.65723</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>6049.586776</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>6134.768198</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>5962.926204</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>6261.236879</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>5957.002178</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>5837.810359</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>5848.272547</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>5825.413783</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>5594.716278</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>5875.899369</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>5899.02192</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>5596.107498</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>5809.670986</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>5678.573385</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>5847.979977</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>5684.630861</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>5907.116012</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>5731.169803</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>5555.742419</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>5865.381178</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>5469.311329</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>5836.215921</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>5928.154933</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>5739.260742</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>5543.044862</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>5454.151233</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>5378.952627</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>5716.087704</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>5834.86643</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>5903.056925</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>6072.051975</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>5376.519502</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>5676.067853</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>5692.271533</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>5526.650452</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>5357.441959</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>5824.580241</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>5539.361853</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>5559.224137</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>5547.215673</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>5487.173952</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>5475.437592</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>5720.601352</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>5731.80292</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>5533.24777</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>5787.422061</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>5381.782804</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>6044.034852</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>5682.978187</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>5556.942812</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>5581.686926</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>5852.225803</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>6218.545423</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>5592.196228</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>5713.153884</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>5803.603542</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>6261.093326</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>5739.727004</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>5938.466888</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>5784.184366</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>5789.587099</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>5756.151728</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>6272.663644</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>6137.706472</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>5945.781225</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>5443.754594</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>5542.216439</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>5965.34524</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>6084.097547</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>5617.37325</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>5367.041899</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>5609.377723</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>5410.65131</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>5827.349714</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>5587.003773</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>5522.855497</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>5607.681021</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>5553.026109</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>5974.382124</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>5473.503807</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>5708.40649</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>6192.890522</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>5576.862842</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>6109.056226</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>6033.801367</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>5741.485633</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>5668.248773</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>6441.29773</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>5784.416511</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>6132.622026</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>5792.718033</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>6072.950188</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>5950.92191</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>5970.91888</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>6007.394733</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>6150.607346</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>5941.958933</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>5719.437461</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>6080.326534</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>6250.373228</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>5755.512773</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>5958.958565</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>6153.790403</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>6251.619092</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>6327.709759</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>5999.318936</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>6156.025312</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>6125.228428</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>6084.607962</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>6224.248536</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>6486.407524</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>6589.284487</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>6047.785504</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>6055.369393</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>6676.688761</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>6132.156467</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>6005.708713</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>6284.736843</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>6447.672225</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>6786.904072</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>5966.503941</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>5875.692615</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>6161.462604</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>6008.415295</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>6207.322623</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>6155.317645</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>5815.073294</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>6258.627565</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>6264.339328</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>6075.484618</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>5997.149846</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>6258.995698</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>6098.513023</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>5967.545808</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>6050.210057</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>5869.435514</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>6411.662543</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>5981.215163</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>6329.613916</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>5641.79707</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>5915.410448</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>5977.88942</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>5492.009542</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>6475.853847</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>6348.926965</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>5621.029712</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>6013.508865</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>5783.302333</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>5887.950004</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>6238.88987</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>6153.656904</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>6129.960267</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>6088.09154</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>5885.130316</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>6196.519257</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>5939.447398</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>5911.654356</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>6247.775761</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>6020.04991</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>6327.788387</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>6174.507664</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>5871.901572</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>6522.031534</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>6277.599997</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>5925.4793</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>6481.954448</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>6060.774366</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>6274.395688</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>6089.291776</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>6443.491024</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>5787.414943</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>6313.482316</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>6389.312094</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>6219.583264</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>5979.200204</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>6249.067001</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>6501.978033</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>6593.508092</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>6323.661729</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>6319.346323</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>6383.363617</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>6435.536448</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>6643.009678</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>6831.157558</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>6890.767709</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>6806.586846</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>6204.656266</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>6273.026835</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>6637.463746</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>6446.603943</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>6646.614562</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>6297.642003</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>6286.658567</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>6744.51071</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>6597.854656</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>6841.94411</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>6310.575852</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>6491.502228</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>6714.155913</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>6554.719392</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>6529.378454</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>6288.824618</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>6233.300036</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>6992.777102</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>6561.219281</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>6185.329471</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>6853.063088</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>6235.143374</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>6749.366219</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>6787.093651</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>6375.862813</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>6251.133709</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>6634.499075</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>7020.198265</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>6477.444109</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>6625.507409</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>6756.639597</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>7128.110798</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>6408.929305</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>6719.068817</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>6857.880709</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>6705.886663</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>6695.069079</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>6823.21957</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>6758.372238</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>6238.096511</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>6056.145008</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>6377.758848</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>6359.688085</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>6851.36504</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>6440.395457</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>6779.881126</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>6267.735953</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>6440.291017</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>6839.074716</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>6480.193426</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>6501.59856</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>7070.021991</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>6648.940903</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>6555.886339</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>6230.282146</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>6869.281711</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>6867.131017</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>6869.394328</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>7009.958353</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>6473.120605</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>7089.764396</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>6742.623843</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>6559.694613</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>6866.211035</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>6701.295337</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>6681.224432</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>6939.665041</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>7031.508713</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>6742.311944</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>6463.494374</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>6488.530375</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>6915.103169</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>6606.753545</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>6936.019301</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>6211.014221</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>6293.057904</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>6716.790878</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>6729.184718</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>6334.677884</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>6498.553782</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>6518.189492</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>6824.426905</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>6651.235546</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>6635.560064</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>6781.117629</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>6512.057205</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>6638.128393</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>6819.202456</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>6890.0561</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>6563.342769</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>6713.363519</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>6554.005743</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>6572.124482</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>6442.135111</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>6221.070814</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>6842.840682</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>6754.190118</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>6201.557598</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>6438.324539</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>6262.685971</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>6936.270286</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>6707.755684</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>6270.100945</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>6781.523532</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>6019.390066</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>6306.458499</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>6319.265708</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>6187.485218</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>6436.987041</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>6092.736498</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>5835.504672</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>6155.606774</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>6446.156533</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>6009.77171</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>6085.866907</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>6046.839685</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>6512.370996</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>6137.206849</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>6060.41534</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>5775.358385</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>6240.351313</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>6045.399008</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>5861.291942</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>5666.555079</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>5665.438582</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>5879.012959</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>6238.404926</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>5488.266688</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>5415.721672</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>5295.240134</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>5522.564834</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>5393.717209</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>5059.940782</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>5163.511817</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>5298.861653</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>5268.239859</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>5428.823899</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>5207.722347</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>5225.004697</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>5019.835902</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>4883.30658</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>5729.98621</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>5060.204707</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>4985.51279</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>4832.532426</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>4771.648938</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>5067.436277</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>4942.483856</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>5314.62026</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>5254.690669</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>5174.536012</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>5753.119806</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>4989.733807</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>5746.966935</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>4878.220961</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>5143.156087</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>4947.377954</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>5265.962796</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>5308.535316</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>5230.430743</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>5290.517482</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>5288.822022</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>5095.432144</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>5551.192694</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>5275.807589</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>5527.882844</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>5964.253675</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>5357.133979</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>5369.35448</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>5989.881275</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>5584.752526</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>5504.763418</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>5477.248035</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>5522.030545</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>5615.649478</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>5827.223175</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>5457.13245</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>5938.562564</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>5484.147426</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>5537.207267</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>5481.751737</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>5719.079451</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>5768.459576</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>5685.225055</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>5697.365852</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>5811.850326</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>5589.890016</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>5974.924059</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>5780.89635</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>5764.454928</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>5654.35924</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>5495.787848</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>6338.128476</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>5745.523436</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>5483.720499</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>5611.594257</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>5662.451654</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>5854.320282</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>5536.653543</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>5860.119369</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>6081.063506</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>5733.492623</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>5752.079129</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>5566.236675</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>6088.11404</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>6074.463448</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>5690.849304</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>5830.221092</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>5686.236226</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>6165.097816</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>5764.64222</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>5993.276711</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>5843.053667</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>5832.84671</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>6343.608868</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>6411.312552</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>6572.453321</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>6409.062744</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>6052.176191</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>6474.077613</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>6573.196397</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>6655.910861</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>6275.733101</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>6253.145097</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>6234.966822</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>6459.206186</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>6622.070213</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>6638.389162</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>6415.017626</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>6799.664787</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>6823.598714</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>6872.98686</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>6664.490426</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>6878.016871</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>7199.025619</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>6826.986871</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>6838.943797</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>6731.729943</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>6800.285247</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>6857.2776</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>6936.271295</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>6625.288393</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>6501.655159</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>6545.909101</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="552514518"/>
+        <c:axId val="168581047"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="552514518"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="168581047"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="168581047"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="552514518"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="0" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>285115</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3365500" y="69850"/>
+        <a:ext cx="7816215" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>304165</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3371850" y="2901950"/>
+        <a:ext cx="7828915" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>863600</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3321050" y="5772150"/>
+        <a:ext cx="7905750" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6985</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>368300</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3359785" y="8572500"/>
+        <a:ext cx="7905115" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8455,5 +17821,6 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>